--- a/stories/arbres/TREE-AUT-034.xlsx
+++ b/stories/arbres/TREE-AUT-034.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Kenzo est avec papa, dans le jardin. Kenzo a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo écoute papa. Kenzo entend les mots : ranger, caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-034.xlsx
+++ b/stories/arbres/TREE-AUT-034.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Kenzo est avec papa, dans le jardin. Kenzo a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo écoute papa. Kenzo entend les mots : ranger, caisse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Kenzo rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Kenzo rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Kenzo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Kenzo rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Kenzo rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Kenzo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Kenzo rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Kenzo rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Kenzo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Kenzo rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Kenzo rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Kenzo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Kenzo rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Kenzo rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Kenzo rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Kenzo rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Kenzo rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-034.xlsx
+++ b/stories/arbres/TREE-AUT-034.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ranger après le jeu — dans le jardin</t>
+          <t>L'escargot sous le prunier</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un escargot avance sous le prunier. Amir joue. Après le jeu, il met les jouets dans la caisse en bois.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Kenzo est avec papa, dans le jardin. Kenzo a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo écoute papa. Kenzo entend les mots : ranger, caisse.</t>
+          <t>Un prunier penche au fond du jardin. Une feuille brille, encore mouillée. Un escargot avance dessus, tout lent. La pomme d'arrosoir goutte. Ploc, sur la terre sombre. Une caisse en bois attend sous l'arbre. La corde de la caisse est un peu rêche. Des pinces à linge dansent sur le fil. Un torchon rayé sèche, tout léger. Papa pose les bottes près du pas de la porte. Maman accroche encore une pince. Tu as vu l'escargot, Amir ? Oui. Il est tout petit. La caisse t'attend sous le prunier. En ce moment, Amir touche la corde. Le bois est lisse, un peu frais. Je veux jouer ! D'accord. On joue. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. Tu t'en souviens. L'escargot avance encore d'un tout petit pas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,32 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Kenzo est avec papa, dans le jardin. Kenzo a envie de jouer. papa est là, tout près. On va apprendre : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo écoute papa. Kenzo entend les mots : ranger, caisse.</t>
+          <t>narrateur|Un prunier penche au fond du jardin.
+narrateur|Une feuille brille, encore mouillée.
+narrateur|Un escargot avance dessus, tout lent.
+narrateur|La pomme d'arrosoir goutte.
+narrateur|Ploc, sur la terre sombre.
+narrateur|Une caisse en bois attend sous l'arbre.
+narrateur|La corde de la caisse est un peu rêche.
+narrateur|Des pinces à linge dansent sur le fil.
+narrateur|Un torchon rayé sèche, tout léger.
+narrateur|Papa pose les bottes près du pas de la porte.
+narrateur|Maman accroche encore une pince.
+maman|Tu as vu l'escargot, Amir ?
+enfant-m|Oui.
+enfant-m|Il est tout petit.
+papa|La caisse t'attend sous le prunier.
+narrateur|En ce moment, Amir touche la corde.
+narrateur|Le bois est lisse, un peu frais.
+enfant-m|Je veux jouer !
+maman|D'accord.
+maman|On joue.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+papa|Tu t'en souviens.
+narrateur|L'escargot avance encore d'un tout petit pas.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1390,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Amir peut jouer à trois endroits. La cuisine, le jardin, ou la chambre ? Tu choisis. Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1554,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Amir peut jouer à trois endroits.
+papa|La cuisine, le jardin, ou la chambre ?
+maman|Tu choisis.
+maman|Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Amir pousse la porte de la cuisine. Les carreaux sont froids sous les pieds. Ça sent la confiture de prunes. Une cuillère de bois est un peu collante. Une mouche se pose sur la vitre. Puis elle s'en va. Ça sent les prunes, papa. C'est la confiture. Tu peux jouer ici un moment. La caisse en bois est près du buffet. La corde de la caisse est un peu rêche. Tu joues. Puis on range. Ranger, c'est mettre dans la caisse. Dans la caisse. Bravo. Tu t'en souviens. Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,8 +1725,24 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On souffle doucement.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Amir pousse la porte de la cuisine.
+narrateur|Les carreaux sont froids sous les pieds.
+narrateur|Ça sent la confiture de prunes.
+narrateur|Une cuillère de bois est un peu collante.
+narrateur|Une mouche se pose sur la vitre.
+narrateur|Puis elle s'en va.
+enfant-m|Ça sent les prunes, papa.
+papa|C'est la confiture.
+maman|Tu peux jouer ici un moment.
+narrateur|La caisse en bois est près du buffet.
+narrateur|La corde de la caisse est un peu rêche.
+papa|Tu joues.
+papa|Puis on range.
+maman|Ranger, c'est mettre dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+papa|Tu t'en souviens.
+narrateur|Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Ranger après le jeu.</t>
+          <t>Amir a joué dans la cuisine. Après le jeu, on fait quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1930,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
+          <t>narrateur|Amir a joué dans la cuisine.
+maman|Après le jeu, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+          <t>Oui. On range. On met dans la caisse. Dans la caisse. Bravo, Amir. Tu as fait du bon travail. La caisse en bois est près du buffet. Une goutte de confiture brille sur la cuillère. On continue ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2103,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Une goutte de confiture brille sur la cuillère.
+maman|On continue ensemble.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2139,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Dans la cuisine, Amir prend un jeu. Les cubes, le livre, ou la dînette ? Tu choisis. Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2303,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Dans la cuisine, Amir prend un jeu.
+papa|Les cubes, le livre, ou la dînette ?
+maman|Tu choisis.
+maman|Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2334,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Dans la cuisine, les cubes de bois sont en tas. Un cube jaune est lisse. Un cube vert est un peu rêche. Les cubes, papa. D'accord. Amir pose une petite tour. Clic. Encore clic. Tu joues un moment. La tour est petite, toute fière. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. Un cube jaune a une miette de prune. La caisse en bois est près du buffet. Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,7 +2474,23 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, les cubes de bois sont en tas.
+narrateur|Un cube jaune est lisse.
+narrateur|Un cube vert est un peu rêche.
+enfant-m|Les cubes, papa.
+papa|D'accord.
+narrateur|Amir pose une petite tour.
+narrateur|Clic.
+narrateur|Encore clic.
+maman|Tu joues un moment.
+narrateur|La tour est petite, toute fière.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|Un cube jaune a une miette de prune.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2434,7 +2518,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a les cubes, dans la cuisine. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2682,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a les cubes, dans la cuisine.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2713,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans la cuisine. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Un cube a un peu de confiture au coin. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,7 +2853,28 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans la cuisine.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Un cube a un peu de confiture au coin.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2794,7 +2902,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec les cubes. C'était le matin. Un cube a un peu de confiture au coin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3042,14 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Un cube a un peu de confiture au coin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3077,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans la cuisine. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Les cubes sont encore tièdes, côté soleil. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3217,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans la cuisine.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Les cubes sont encore tièdes, côté soleil.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3266,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec les cubes. C'était après la sieste. Les cubes sont encore tièdes, côté soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3406,14 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Les cubes sont encore tièdes, côté soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3441,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans la cuisine. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La cuillère de bois sèche près du buffet. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,7 +3581,28 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans la cuisine.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La cuillère de bois sèche près du buffet.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3466,7 +3630,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec les cubes. C'était le soir. La cuillère de bois sèche près du buffet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3770,14 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|La cuillère de bois sèche près du buffet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3805,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>Dans la cuisine, le livre est ouvert, tout plat. La couverture est lisse, un peu froide. Les pages sentent le papier. Le livre, maman. D'accord. Amir tourne une page, tout doux. Le papier chuchote. Tu joues un moment. Sur la page, il y a un bateau rouge. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. Une page du livre sent la confiture. La caisse en bois est près du buffet. Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,7 +3945,22 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, le livre est ouvert, tout plat.
+narrateur|La couverture est lisse, un peu froide.
+narrateur|Les pages sentent le papier.
+enfant-m|Le livre, maman.
+papa|D'accord.
+narrateur|Amir tourne une page, tout doux.
+narrateur|Le papier chuchote.
+maman|Tu joues un moment.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|Une page du livre sent la confiture.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3802,7 +3988,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a le livre, dans la cuisine. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3966,7 +4152,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a le livre, dans la cuisine.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3994,7 +4183,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans la cuisine. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Une page du livre sent la prune. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4134,7 +4323,28 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans la cuisine.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Une page du livre sent la prune.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4162,7 +4372,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec le livre. C'était le matin. Une page du livre sent la prune. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4302,7 +4512,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Une page du livre sent la prune.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4330,7 +4547,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans la cuisine. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Le bateau rouge dort dans la caisse. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4470,7 +4687,28 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans la cuisine.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Le bateau rouge dort dans la caisse.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4498,7 +4736,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec le livre. C'était après la sieste. Le bateau rouge dort dans la caisse. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4638,7 +4876,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Le bateau rouge dort dans la caisse.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4666,7 +4911,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans la cuisine. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La vitre de cuisine a une goutte. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4806,7 +5051,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans la cuisine.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La vitre de cuisine a une goutte.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4834,7 +5100,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec le livre. C'était le soir. La vitre de cuisine a une goutte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4974,7 +5240,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|La vitre de cuisine a une goutte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5002,7 +5275,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Dans la cuisine, la dînette cliquette dans son panier. Une petite assiette est blanche. Une tasse est tiède. La dînette, papa. D'accord. Amir pose la tasse près de l'assiette. Ting. Tu joues un moment. Une cuillère minuscule brille. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. La petite tasse a un cercle collant. La caisse en bois est près du buffet. Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5142,7 +5415,22 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, la dînette cliquette dans son panier.
+narrateur|Une petite assiette est blanche.
+narrateur|Une tasse est tiède.
+enfant-m|La dînette, papa.
+papa|D'accord.
+narrateur|Amir pose la tasse près de l'assiette.
+narrateur|Ting.
+maman|Tu joues un moment.
+narrateur|Une cuillère minuscule brille.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|La petite tasse a un cercle collant.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Une goutte de confiture brille sur la cuillère.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5170,7 +5458,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a la dînette, dans la cuisine. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5334,7 +5622,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a la dînette, dans la cuisine.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5362,7 +5653,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans la cuisine. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La petite tasse est encore un peu collante. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5502,7 +5793,28 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans la cuisine.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La petite tasse est encore un peu collante.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5530,7 +5842,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec la dînette. C'était le matin. La petite tasse est encore un peu collante. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5670,7 +5982,14 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|La petite tasse est encore un peu collante.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5698,7 +6017,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans la cuisine. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Une cuillère minuscule brille dans la caisse. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5838,7 +6157,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans la cuisine.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Une cuillère minuscule brille dans la caisse.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5866,7 +6206,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec la dînette. C'était après la sieste. Une cuillère minuscule brille dans la caisse. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6006,7 +6346,14 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|Une cuillère minuscule brille dans la caisse.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6034,7 +6381,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans la cuisine. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près du buffet. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La casserole de confiture ne chante plus. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6174,7 +6521,28 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans la cuisine.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près du buffet.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La casserole de confiture ne chante plus.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6202,7 +6570,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la cuisine. Il a joué avec la dînette. C'était le soir. La casserole de confiture ne chante plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6342,7 +6710,14 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|La casserole de confiture ne chante plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6370,7 +6745,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Amir revient sous le prunier. La terre est encore un peu molle. L'escargot a avancé d'une feuille. La pomme d'arrosoir goutte encore. Ploc, sur une pierre chaude. Une pince à linge claque une fois. L'escargot est tout petit. Il va tout lentement. Tu peux jouer ici un moment. La caisse en bois est sous le prunier. La corde de la caisse est un peu rêche. Tu joues. Puis on range. Ranger, c'est mettre dans la caisse. Dans la caisse. Bravo. Tu t'en souviens. Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6510,8 +6885,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On écoute jusqu'au bout.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Amir revient sous le prunier.
+narrateur|La terre est encore un peu molle.
+narrateur|L'escargot a avancé d'une feuille.
+narrateur|La pomme d'arrosoir goutte encore.
+narrateur|Ploc, sur une pierre chaude.
+narrateur|Une pince à linge claque une fois.
+enfant-m|L'escargot est tout petit.
+papa|Il va tout lentement.
+maman|Tu peux jouer ici un moment.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|La corde de la caisse est un peu rêche.
+papa|Tu joues.
+papa|Puis on range.
+maman|Ranger, c'est mettre dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+papa|Tu t'en souviens.
+narrateur|Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6539,7 +6930,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Ranger après le jeu.</t>
+          <t>Amir a joué dans le jardin. Après le jeu, on fait quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6699,7 +7090,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
+          <t>narrateur|Amir a joué dans le jardin.
+maman|Après le jeu, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6727,7 +7119,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+          <t>Oui. On range. On met dans la caisse. Dans la caisse. Bravo, Amir. Tu as fait du bon travail. La caisse en bois est sous le prunier. Une feuille mouillée brille encore. On continue ensemble.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6871,7 +7263,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Une feuille mouillée brille encore.
+maman|On continue ensemble.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6899,7 +7299,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Dans le jardin, Amir prend un jeu. Les cubes, le livre, ou la dînette ? Tu choisis. Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7063,7 +7463,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Dans le jardin, Amir prend un jeu.
+papa|Les cubes, le livre, ou la dînette ?
+maman|Tu choisis.
+maman|Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7091,7 +7494,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Dans le jardin, les cubes de bois sont en tas. Un cube jaune est lisse. Un cube vert est un peu rêche. Les cubes, papa. D'accord. Amir pose une petite tour. Clic. Encore clic. Tu joues un moment. La tour est petite, toute fière. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. Un cube a un grain de terre au coin. La caisse en bois est sous le prunier. Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7231,7 +7634,23 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, les cubes de bois sont en tas.
+narrateur|Un cube jaune est lisse.
+narrateur|Un cube vert est un peu rêche.
+enfant-m|Les cubes, papa.
+papa|D'accord.
+narrateur|Amir pose une petite tour.
+narrateur|Clic.
+narrateur|Encore clic.
+maman|Tu joues un moment.
+narrateur|La tour est petite, toute fière.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|Un cube a un grain de terre au coin.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7259,7 +7678,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a les cubes, dans le jardin. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7423,7 +7842,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a les cubes, dans le jardin.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7451,7 +7873,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans le jardin. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Un cube a un grain de terre au coin. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7591,7 +8013,28 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans le jardin.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Un cube a un grain de terre au coin.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7619,7 +8062,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec les cubes. C'était le matin. Un cube a un grain de terre au coin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7759,7 +8202,14 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Un cube a un grain de terre au coin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7787,7 +8237,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans le jardin. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. L'escargot a avancé d'encore une feuille. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7927,7 +8377,28 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans le jardin.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|L'escargot a avancé d'encore une feuille.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7955,7 +8426,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec les cubes. C'était après la sieste. L'escargot a avancé d'encore une feuille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8095,7 +8566,14 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|L'escargot a avancé d'encore une feuille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8123,7 +8601,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans le jardin. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La pomme d'arrosoir s'est tue. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8263,7 +8741,28 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans le jardin.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La pomme d'arrosoir s'est tue.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8291,7 +8790,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec les cubes. C'était le soir. La pomme d'arrosoir s'est tue. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8431,7 +8930,14 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|La pomme d'arrosoir s'est tue.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8459,7 +8965,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>Dans le jardin, le livre est ouvert, tout plat. La couverture est lisse, un peu froide. Les pages sentent le papier. Le livre, maman. D'accord. Amir tourne une page, tout doux. Le papier chuchote. Tu joues un moment. Sur la page, il y a un bateau rouge. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. Une feuille mouillée colle au livre. La caisse en bois est sous le prunier. Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8599,7 +9105,22 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, le livre est ouvert, tout plat.
+narrateur|La couverture est lisse, un peu froide.
+narrateur|Les pages sentent le papier.
+enfant-m|Le livre, maman.
+papa|D'accord.
+narrateur|Amir tourne une page, tout doux.
+narrateur|Le papier chuchote.
+maman|Tu joues un moment.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|Une feuille mouillée colle au livre.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8627,7 +9148,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a le livre, dans le jardin. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8791,7 +9312,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a le livre, dans le jardin.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8819,7 +9343,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans le jardin. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Une page sent l'herbe mouillée. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8959,7 +9483,28 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans le jardin.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Une page sent l'herbe mouillée.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8987,7 +9532,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec le livre. C'était le matin. Une page sent l'herbe mouillée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9127,7 +9672,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Une page sent l'herbe mouillée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9155,7 +9707,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans le jardin. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Le bateau rouge a une ombre de feuille. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9295,7 +9847,28 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans le jardin.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Le bateau rouge a une ombre de feuille.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9323,7 +9896,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec le livre. C'était après la sieste. Le bateau rouge a une ombre de feuille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9463,7 +10036,14 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Le bateau rouge a une ombre de feuille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9491,7 +10071,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans le jardin. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Une pince à linge claque une fois, sur le fil. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9631,7 +10211,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans le jardin.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Une pince à linge claque une fois, sur le fil.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9659,7 +10260,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec le livre. C'était le soir. Une pince à linge claque une fois, sur le fil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9799,7 +10400,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|Une pince à linge claque une fois, sur le fil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9827,7 +10435,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Dans le jardin, la dînette cliquette dans son panier. Une petite assiette est blanche. Une tasse est tiède. La dînette, papa. D'accord. Amir pose la tasse près de l'assiette. Ting. Tu joues un moment. Une cuillère minuscule brille. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. La petite assiette a pris une goutte. La caisse en bois est sous le prunier. Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9967,7 +10575,22 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, la dînette cliquette dans son panier.
+narrateur|Une petite assiette est blanche.
+narrateur|Une tasse est tiède.
+enfant-m|La dînette, papa.
+papa|D'accord.
+narrateur|Amir pose la tasse près de l'assiette.
+narrateur|Ting.
+maman|Tu joues un moment.
+narrateur|Une cuillère minuscule brille.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|La petite assiette a pris une goutte.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Une feuille mouillée brille encore.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9995,7 +10618,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a la dînette, dans le jardin. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10159,7 +10782,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a la dînette, dans le jardin.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10187,7 +10813,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans le jardin. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La petite assiette a une goutte de rosée. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10327,7 +10953,28 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans le jardin.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La petite assiette a une goutte de rosée.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10355,7 +11002,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec la dînette. C'était le matin. La petite assiette a une goutte de rosée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10495,7 +11142,14 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|La petite assiette a une goutte de rosée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10523,7 +11177,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans le jardin. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La tasse a pris un peu de soleil. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10663,7 +11317,28 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans le jardin.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La tasse a pris un peu de soleil.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10691,7 +11366,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec la dînette. C'était après la sieste. La tasse a pris un peu de soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10831,7 +11506,14 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|La tasse a pris un peu de soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10859,7 +11541,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans le jardin. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est sous le prunier. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Le prunier penche, tout calme, au-dessus de la caisse. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10999,7 +11681,28 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans le jardin.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est sous le prunier.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Le prunier penche, tout calme, au-dessus de la caisse.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11027,7 +11730,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans le jardin. Il a joué avec la dînette. C'était le soir. Le prunier penche, tout calme, au-dessus de la caisse. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11167,7 +11870,14 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|Le prunier penche, tout calme, au-dessus de la caisse.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11195,7 +11905,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Amir entre dans la chambre. Le rideau a des feuilles imprimées. Un rayon passe entre deux plis. Les chaussons sont près du lit. L'oreiller est encore un peu tiède. Un bouton de bois brille sur le rideau. Le rideau a des feuilles, maman. Comme le prunier. Tu peux jouer ici un moment. La caisse en bois est près des chaussons. La corde de la caisse est un peu rêche. Tu joues. Puis on range. Ranger, c'est mettre dans la caisse. Dans la caisse. Bravo. Tu t'en souviens. Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11335,8 +12045,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Kenzo se souvient : ranger, caisse. Voici le geste : mettre dans la caisse. On attend son tour.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Amir entre dans la chambre.
+narrateur|Le rideau a des feuilles imprimées.
+narrateur|Un rayon passe entre deux plis.
+narrateur|Les chaussons sont près du lit.
+narrateur|L'oreiller est encore un peu tiède.
+narrateur|Un bouton de bois brille sur le rideau.
+enfant-m|Le rideau a des feuilles, maman.
+papa|Comme le prunier.
+maman|Tu peux jouer ici un moment.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|La corde de la caisse est un peu rêche.
+papa|Tu joues.
+papa|Puis on range.
+maman|Ranger, c'est mettre dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+papa|Tu t'en souviens.
+narrateur|Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11364,7 +12090,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Ranger après le jeu.</t>
+          <t>Amir a joué dans la chambre. Après le jeu, on fait quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11524,7 +12250,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Ranger après le jeu.</t>
+          <t>narrateur|Amir a joué dans la chambre.
+maman|Après le jeu, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11552,7 +12279,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+          <t>Oui. On range. On met dans la caisse. Dans la caisse. Bravo, Amir. Tu as fait du bon travail. La caisse en bois est près des chaussons. Un pli du rideau bouge un peu. On continue ensemble.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11696,7 +12423,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans la caisse. Kenzo respire. Kenzo retient : ranger, caisse. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Un pli du rideau bouge un peu.
+maman|On continue ensemble.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11724,7 +12459,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Dans la chambre, Amir prend un jeu. Les cubes, le livre, ou la dînette ? Tu choisis. Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11888,7 +12623,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Dans la chambre, Amir prend un jeu.
+papa|Les cubes, le livre, ou la dînette ?
+maman|Tu choisis.
+maman|Ensuite on met dans la caisse.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11916,7 +12654,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Dans la chambre, les cubes de bois sont en tas. Un cube jaune est lisse. Un cube vert est un peu rêche. Les cubes, papa. D'accord. Amir pose une petite tour. Clic. Encore clic. Tu joues un moment. La tour est petite, toute fière. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. Un cube glisse près d'un chausson. La caisse en bois est près des chaussons. Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12056,7 +12794,23 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, les cubes de bois sont en tas.
+narrateur|Un cube jaune est lisse.
+narrateur|Un cube vert est un peu rêche.
+enfant-m|Les cubes, papa.
+papa|D'accord.
+narrateur|Amir pose une petite tour.
+narrateur|Clic.
+narrateur|Encore clic.
+maman|Tu joues un moment.
+narrateur|La tour est petite, toute fière.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|Un cube glisse près d'un chausson.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12084,7 +12838,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a les cubes, dans la chambre. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12248,7 +13002,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a les cubes, dans la chambre.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12276,7 +13033,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans la chambre. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Un cube a glissé près d'un chausson. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12416,7 +13173,28 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans la chambre.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Un cube a glissé près d'un chausson.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12444,7 +13222,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec les cubes. C'était le matin. Un cube a glissé près d'un chausson. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12584,7 +13362,14 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Un cube a glissé près d'un chausson.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12612,7 +13397,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans la chambre. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Les cubes sont tièdes, côté oreiller. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12752,7 +13537,28 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans la chambre.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Les cubes sont tièdes, côté oreiller.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12780,7 +13586,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec les cubes. C'était après la sieste. Les cubes sont tièdes, côté oreiller. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12920,7 +13726,14 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Les cubes sont tièdes, côté oreiller.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12948,7 +13761,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans la chambre. La tour est petite, toute fière. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir met les cubes dans la caisse. Toc, le bois répond. Les cubes font toc, dans le bois. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Le rideau à feuilles ne bouge plus. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13088,7 +13901,28 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans la chambre.
+narrateur|La tour est petite, toute fière.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir met les cubes dans la caisse.
+narrateur|Toc, le bois répond.
+narrateur|Les cubes font toc, dans le bois.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Le rideau à feuilles ne bouge plus.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13116,7 +13950,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec les cubes. C'était le soir. Le rideau à feuilles ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13256,7 +14090,14 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|Le rideau à feuilles ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13284,7 +14125,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>Dans la chambre, le livre est ouvert, tout plat. La couverture est lisse, un peu froide. Les pages sentent le papier. Le livre, maman. D'accord. Amir tourne une page, tout doux. Le papier chuchote. Tu joues un moment. Sur la page, il y a un bateau rouge. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. Le bateau rouge a l'ombre du rideau. La caisse en bois est près des chaussons. Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13424,7 +14265,22 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, le livre est ouvert, tout plat.
+narrateur|La couverture est lisse, un peu froide.
+narrateur|Les pages sentent le papier.
+enfant-m|Le livre, maman.
+papa|D'accord.
+narrateur|Amir tourne une page, tout doux.
+narrateur|Le papier chuchote.
+maman|Tu joues un moment.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|Le bateau rouge a l'ombre du rideau.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13452,7 +14308,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a le livre, dans la chambre. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13616,7 +14472,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a le livre, dans la chambre.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13644,7 +14503,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans la chambre. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Une page du livre touche un chausson. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13784,7 +14643,28 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans la chambre.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Une page du livre touche un chausson.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13812,7 +14692,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec le livre. C'était le matin. Une page du livre touche un chausson. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13952,7 +14832,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Une page du livre touche un chausson.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13980,7 +14867,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans la chambre. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Le bateau rouge est dans l'ombre du rideau. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14120,7 +15007,28 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans la chambre.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Le bateau rouge est dans l'ombre du rideau.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14148,7 +15056,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec le livre. C'était après la sieste. Le bateau rouge est dans l'ombre du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14288,7 +15196,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Le bateau rouge est dans l'ombre du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14316,7 +15231,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans la chambre. Sur la page, il y a un bateau rouge. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir ferme le livre. Il le met dans la caisse. Le livre pose un tout petit bruit, plat. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La petite lampe de chevet attend. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14456,7 +15371,28 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans la chambre.
+narrateur|Sur la page, il y a un bateau rouge.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir ferme le livre.
+narrateur|Il le met dans la caisse.
+narrateur|Le livre pose un tout petit bruit, plat.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La petite lampe de chevet attend.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14484,7 +15420,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec le livre. C'était le soir. La petite lampe de chevet attend. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14624,7 +15560,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|La petite lampe de chevet attend.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14652,7 +15595,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Dans la chambre, la dînette cliquette dans son panier. Une petite assiette est blanche. Une tasse est tiède. La dînette, papa. D'accord. Amir pose la tasse près de l'assiette. Ting. Tu joues un moment. Une cuillère minuscule brille. Après le jeu, on range. On met dans la caisse. Dans la caisse. Bravo. La petite cuillère brille près du lit. La caisse en bois est près des chaussons. Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14792,7 +15735,22 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : mettre dans la caisse. Kenzo répète tout bas : ranger, caisse. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, la dînette cliquette dans son panier.
+narrateur|Une petite assiette est blanche.
+narrateur|Une tasse est tiède.
+enfant-m|La dînette, papa.
+papa|D'accord.
+narrateur|Amir pose la tasse près de l'assiette.
+narrateur|Ting.
+maman|Tu joues un moment.
+narrateur|Une cuillère minuscule brille.
+papa|Après le jeu, on range.
+maman|On met dans la caisse.
+enfant-m|Dans la caisse.
+papa|Bravo.
+narrateur|La petite cuillère brille près du lit.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Un pli du rideau bouge un peu.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14820,7 +15778,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Amir a la dînette, dans la chambre. On range à quelle heure ? Le matin, après la sieste, ou le soir ? Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14984,7 +15942,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Amir a la dînette, dans la chambre.
+maman|On range à quelle heure ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|Ensuite, tout va dans la caisse.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15012,7 +15973,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, un peu bleue. Dehors, un oiseau chante une fois. L'air touche le nez, tout frais. Amir est encore dans la chambre. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range, puis la journée continue. J'ai rangé le matin. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. La petite tasse est froide, près des chaussons. La lumière pâle reste sur le bois. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15152,7 +16113,28 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le matin. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Dehors, un oiseau chante une fois.
+narrateur|L'air touche le nez, tout frais.
+narrateur|Amir est encore dans la chambre.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range, puis la journée continue.
+enfant-m|J'ai rangé le matin.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|La petite tasse est froide, près des chaussons.
+narrateur|La lumière pâle reste sur le bois.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15180,7 +16162,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec la dînette. C'était le matin. La petite tasse est froide, près des chaussons. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15320,7 +16302,14 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|La petite tasse est froide, près des chaussons.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15348,7 +16337,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Amir a une joue un peu marquée. L'air de la maison est tiède. Une bande d'ombre traverse le sol. Amir est encore dans la chambre. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range, tout doucement. J'ai rangé après la sieste. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. Une cuillère minuscule a glissé sous le pli du rideau. Amir la met dans la caisse. La bande d'ombre a bougé un peu. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15488,7 +16477,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et après la sieste. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Amir a une joue un peu marquée.
+narrateur|L'air de la maison est tiède.
+narrateur|Une bande d'ombre traverse le sol.
+narrateur|Amir est encore dans la chambre.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range, tout doucement.
+enfant-m|J'ai rangé après la sieste.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|Une cuillère minuscule a glissé sous le pli du rideau.
+narrateur|Amir la met dans la caisse.
+narrateur|La bande d'ombre a bougé un peu.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15516,7 +16527,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec la dînette. C'était après la sieste. La cuillère minuscule est dans la caisse. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15656,7 +16667,14 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|La cuillère minuscule est dans la caisse.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15684,7 +16702,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lumière devient orange, toute douce. Une première lampe s'allume au loin. L'air est plus frais sur les joues. Amir est encore dans la chambre. Une cuillère minuscule brille. C'est l'heure de ranger. Après le jeu, on met dans la caisse. La caisse en bois est près des chaussons. Amir met la dînette dans la caisse. La petite assiette glisse, tout doux. La petite tasse fait ting, une dernière fois. On range pour demain. J'ai rangé le soir. Bravo. Tu as rangé. Tu as mis dans la caisse. Tu as fait du bon travail. L'oreiller est plat, près de la caisse pleine. La lampe fait un rond jaune au sol. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15824,7 +16842,28 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le soir. Kenzo a appris : Ranger après le jeu. Voici le geste : mettre dans la caisse. Kenzo a entendu : ranger, caisse. Kenzo dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est le soir.
+narrateur|La lumière devient orange, toute douce.
+narrateur|Une première lampe s'allume au loin.
+narrateur|L'air est plus frais sur les joues.
+narrateur|Amir est encore dans la chambre.
+narrateur|Une cuillère minuscule brille.
+papa|C'est l'heure de ranger.
+maman|Après le jeu, on met dans la caisse.
+narrateur|La caisse en bois est près des chaussons.
+narrateur|Amir met la dînette dans la caisse.
+narrateur|La petite assiette glisse, tout doux.
+narrateur|La petite tasse fait ting, une dernière fois.
+papa|On range pour demain.
+enfant-m|J'ai rangé le soir.
+maman|Bravo.
+maman|Tu as rangé.
+papa|Tu as mis dans la caisse.
+maman|Tu as fait du bon travail.
+narrateur|L'oreiller est plat, près de la caisse pleine.
+narrateur|La lampe fait un rond jaune au sol.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15852,7 +16891,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Amir. Tu as fait du bon travail. Après le jeu, tu as mis dans la caisse. Amir est passé dans la chambre. Il a joué avec la dînette. C'était le soir. L'oreiller est plat, près de la caisse pleine. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15992,7 +17031,14 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Après le jeu, tu as mis dans la caisse.
+narrateur|Amir est passé dans la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|L'oreiller est plat, près de la caisse pleine.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16014,7 +17060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16052,6 +17098,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-034.xlsx
+++ b/stories/arbres/TREE-AUT-034.xlsx
@@ -4593,17 +4593,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Amir tend la corde le long du sillon du râteau. Le torchon s'y couche, en pente douce. Le manche, au mur, ne vole plus le fil. Un chemin d'ombre ! La coquille s'engage dessous, lente. La corde a trouvé mieux qu'un tas. Et le fer a trouvé le mur. L'herbe se relève où le râteau couchait.</t>
+          <t>Amir tend la corde le long de la trace du râteau. Le torchon s'y couche, en pente douce. Le manche, au mur, ne vole plus le fil. Un chemin d'ombre ! La coquille s'engage dessous, lente. La corde a trouvé mieux qu'un tas. Et le fer a trouvé le mur. L'herbe se relève où le râteau couchait.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir tend la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; le long du sillon du râteau. Le torchon s'y couche, en pente douce. Le manche, au mur, ne vole plus le fil. Un chemin d'ombre ! La coquille s'engage dessous, lente. La corde a trouvé mieux qu'un tas. Et le fer a trouvé le mur. L'herbe se relève où le râteau couchait.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir tend la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; le long de la trace du râteau. Le torchon s'y couche, en pente douce. Le manche, au mur, ne vole plus le fil. Un chemin d'ombre ! La coquille s'engage dessous, lente. La corde a trouvé mieux qu'un tas. Et le fer a trouvé le mur. L'herbe se relève où le râteau couchait.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Amir tend la &lt;emphasis&gt;corde&lt;/emphasis&gt; le long du sillon du râteau. Le torchon s'y couche, en pente douce. Le manche, au mur, ne vole plus le fil. Un chemin d'ombre ! La coquille s'engage dessous, lente. La corde a trouvé mieux qu'un tas. Et le fer a trouvé le mur. L'herbe se relève où le râteau couchait. [pause]</t>
+          <t>Amir tend la &lt;emphasis&gt;corde&lt;/emphasis&gt; le long de la trace du râteau. Le torchon s'y couche, en pente douce. Le manche, au mur, ne vole plus le fil. Un chemin d'ombre ! La coquille s'engage dessous, lente. La corde a trouvé mieux qu'un tas. Et le fer a trouvé le mur. L'herbe se relève où le râteau couchait. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Amir tend la corde le long du sillon du râteau.
+          <t>narrateur|Amir tend la corde le long de la trace du râteau.
 narrateur|Le torchon s'y couche, en pente douce.
 narrateur|Le manche, au mur, ne vole plus le fil.
 enfant-m|Un chemin d'ombre !
@@ -4776,17 +4776,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Amir suit du doigt le sillon vide. C'était le chemin du fer. Maintenant, c'est le chemin de la corde. L'herbe va se relever. Le manche au mur ne bouge plus. Sous le tissu, une virgule d'humidité brille.</t>
+          <t>Amir suit du doigt la trace vide. C'était le chemin du fer. Maintenant, c'est le chemin de la corde. L'herbe va se relever. Le manche au mur ne bouge plus. Sous le tissu, une petite trace mouillée brille.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir suit du doigt le sillon vide. C'était le chemin du fer. Maintenant, c'est le chemin de la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt;. L'herbe va se relever. Le manche au mur ne bouge plus. Sous le tissu, une virgule d'humidité brille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir suit du doigt la trace vide. C'était le chemin du fer. Maintenant, c'est le chemin de la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt;. L'herbe va se relever. Le manche au mur ne bouge plus. Sous le tissu, une petite trace mouillée brille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir suit du doigt le sillon vide. C'était le chemin du fer. Maintenant, c'est le chemin de la &lt;emphasis&gt;corde&lt;/emphasis&gt;. L'herbe va se relever. Le manche au mur ne bouge plus. Sous le tissu, une virgule d'humidité brille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir suit du doigt la trace vide. C'était le chemin du fer. Maintenant, c'est le chemin de la &lt;emphasis&gt;corde&lt;/emphasis&gt;. L'herbe va se relever. Le manche au mur ne bouge plus. Sous le tissu, une petite trace mouillée brille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|Amir suit du doigt le sillon vide.
+          <t>narrateur|Amir suit du doigt la trace vide.
 papa|C'était le chemin du fer.
 enfant-m|Maintenant, c'est le chemin de la corde.
 maman|L'herbe va se relever.
 narrateur|Le manche au mur ne bouge plus.
-narrateur|Sous le tissu, une virgule d'humidité brille.</t>
+narrateur|Sous le tissu, une petite trace mouillée brille.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -8140,17 +8140,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Amir s'accroupit devant la porte de pinces. On frappe, avant d'entrer ? On n'entre pas, c'est chez lui. Tes bottes, elles, frappent le paillasson. Deux pinces font des sentinelles têtues. Au fond du bois, rien ne bouge, et c'est bien.</t>
+          <t>Amir s'accroupit devant la porte de pinces. On frappe, avant d'entrer ? On n'entre pas, c'est chez lui. Tes bottes, elles, frappent le paillasson. Deux pinces font des gardes bien droites. Au fond du bois, rien ne bouge, et c'est bien.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir s'accroupit devant la porte de &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt;. On frappe, avant d'entrer ? On n'entre pas, c'est chez lui. Tes bottes, elles, frappent le paillasson. Deux pinces font des sentinelles têtues. Au fond du bois, rien ne bouge, et c'est bien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir s'accroupit devant la porte de &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt;. On frappe, avant d'entrer ? On n'entre pas, c'est chez lui. Tes bottes, elles, frappent le paillasson. Deux pinces font des gardes bien droites. Au fond du bois, rien ne bouge, et c'est bien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir s'accroupit devant la porte de &lt;emphasis&gt;pinces&lt;/emphasis&gt;. On frappe, avant d'entrer ? On n'entre pas, c'est chez lui. Tes bottes, elles, frappent le paillasson. Deux pinces font des sentinelles têtues. Au fond du bois, rien ne bouge, et c'est bien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir s'accroupit devant la porte de &lt;emphasis&gt;pinces&lt;/emphasis&gt;. On frappe, avant d'entrer ? On n'entre pas, c'est chez lui. Tes bottes, elles, frappent le paillasson. Deux pinces font des gardes bien droites. Au fond du bois, rien ne bouge, et c'est bien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
 papa|On frappe, avant d'entrer ?
 enfant-m|On n'entre pas, c'est chez lui.
 maman|Tes bottes, elles, frappent le paillasson.
-narrateur|Deux pinces font des sentinelles têtues.
+narrateur|Deux pinces font des gardes bien droites.
 narrateur|Au fond du bois, rien ne bouge, et c'est bien.</t>
         </is>
       </c>
@@ -8693,17 +8693,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Amir glisse le seau dans l'ouverture de la caisse. Le bleu fait un sas avant le bois. Deux maisons, l'une dans l'autre ! L'escargot choisit d'abord le seau, plus frais. Le seau était vide, il servait à rien. Là, il sert à l'ombre. Une botte sèche au loin, oubliée du drame. Dans le bois, un silence rond.</t>
+          <t>Amir glisse le seau dans l'ouverture de la caisse. Le bleu fait une entrée avant le bois. Deux maisons, l'une dans l'autre ! L'escargot choisit d'abord le seau, plus frais. Le seau était vide, il servait à rien. Là, il sert à l'ombre. Une botte sèche au loin, oubliée du drame. Dans le bois, un silence rond.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir glisse le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; dans l'ouverture de la caisse. Le bleu fait un sas avant le bois. Deux maisons, l'une dans l'autre ! L'escargot choisit d'abord le seau, plus frais. Le seau était vide, il servait à rien. Là, il sert à l'ombre. Une botte sèche au loin, oubliée du drame. Dans le bois, un silence rond.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir glisse le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; dans l'ouverture de la caisse. Le bleu fait une entrée avant le bois. Deux maisons, l'une dans l'autre ! L'escargot choisit d'abord le seau, plus frais. Le seau était vide, il servait à rien. Là, il sert à l'ombre. Une botte sèche au loin, oubliée du drame. Dans le bois, un silence rond.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Amir glisse le &lt;emphasis&gt;seau&lt;/emphasis&gt; dans l'ouverture de la caisse. Le bleu fait un sas avant le bois. Deux maisons, l'une dans l'autre ! L'escargot choisit d'abord le seau, plus frais. Le seau était vide, il servait à rien. Là, il sert à l'ombre. Une botte sèche au loin, oubliée du drame. Dans le bois, un silence rond. [pause]</t>
+          <t>Amir glisse le &lt;emphasis&gt;seau&lt;/emphasis&gt; dans l'ouverture de la caisse. Le bleu fait une entrée avant le bois. Deux maisons, l'une dans l'autre ! L'escargot choisit d'abord le seau, plus frais. Le seau était vide, il servait à rien. Là, il sert à l'ombre. Une botte sèche au loin, oubliée du drame. Dans le bois, un silence rond. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8838,7 +8838,7 @@
       <c r="AW42" t="inlineStr">
         <is>
           <t>narrateur|Amir glisse le seau dans l'ouverture de la caisse.
-narrateur|Le bleu fait un sas avant le bois.
+narrateur|Le bleu fait une entrée avant le bois.
 enfant-m|Deux maisons, l'une dans l'autre !
 narrateur|L'escargot choisit d'abord le seau, plus frais.
 papa|Le seau était vide, il servait à rien.
@@ -8876,17 +8876,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Amir aligne l'arrosoir, le seau, et la caisse du regard. Une famille de contenants ? Le seau pour entrer, la caisse pour dormir. Les bottes pour tes pieds, à la porte. Le bleu du sas capte un rond de ciel. Derrière, le bois reste nuit.</t>
+          <t>Amir aligne l'arrosoir, le seau, et la caisse du regard. L'arrosoir, le seau, et la caisse ? Le seau pour entrer, la caisse pour dormir. Les bottes pour tes pieds, à la porte. Le bleu de l'entrée capte un rond de ciel. Derrière, le bois reste nuit.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir aligne l'arrosoir, le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;, et la caisse du regard. Une famille de contenants ? Le seau pour entrer, la caisse pour dormir. Les bottes pour tes pieds, à la porte. Le bleu du sas capte un rond de ciel. Derrière, le bois reste nuit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir aligne l'arrosoir, le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;, et la caisse du regard. L'arrosoir, le seau, et la caisse ? Le seau pour entrer, la caisse pour dormir. Les bottes pour tes pieds, à la porte. Le bleu de l'entrée capte un rond de ciel. Derrière, le bois reste nuit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir aligne l'arrosoir, le &lt;emphasis&gt;seau&lt;/emphasis&gt;, et la caisse du regard. Une famille de contenants ? Le seau pour entrer, la caisse pour dormir. Les bottes pour tes pieds, à la porte. Le bleu du sas capte un rond de ciel. Derrière, le bois reste nuit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir aligne l'arrosoir, le &lt;emphasis&gt;seau&lt;/emphasis&gt;, et la caisse du regard. L'arrosoir, le seau, et la caisse ? Le seau pour entrer, la caisse pour dormir. Les bottes pour tes pieds, à la porte. Le bleu de l'entrée capte un rond de ciel. Derrière, le bois reste nuit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9025,10 +9025,10 @@
       <c r="AW43" t="inlineStr">
         <is>
           <t>narrateur|Amir aligne l'arrosoir, le seau, et la caisse du regard.
-papa|Une famille de contenants ?
+papa|L'arrosoir, le seau, et la caisse ?
 enfant-m|Le seau pour entrer, la caisse pour dormir.
 maman|Les bottes pour tes pieds, à la porte.
-narrateur|Le bleu du sas capte un rond de ciel.
+narrateur|Le bleu de l'entrée capte un rond de ciel.
 narrateur|Derrière, le bois reste nuit.</t>
         </is>
       </c>
@@ -9447,17 +9447,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Amir plante les pinces de chaque côté de l'entrée. La caisse ouvre une bouche vers l'herbe. Le sillon du râteau passe à côté, vide. Pas de fer dans la porte. L'escargot s'engage, sans un bruit. Les pinces tiennent le rideau d'herbe. Le râteau, au mur, se tait. Un rai de soleil meurt sur le bois.</t>
+          <t>Amir plante les pinces de chaque côté de l'entrée. La caisse ouvre une bouche vers l'herbe. La trace du râteau passe à côté, vide. Pas de fer dans la porte. L'escargot s'engage, sans un bruit. Les pinces tiennent le rideau d'herbe. Le râteau, au mur, se tait. Un rayon de soleil s'arrête sur le bois.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir plante les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; de chaque côté de l'entrée. La caisse ouvre une bouche vers l'herbe. Le sillon du râteau passe à côté, vide. Pas de fer dans la porte. L'escargot s'engage, sans un bruit. Les pinces tiennent le rideau d'herbe. Le râteau, au mur, se tait. Un rai de soleil meurt sur le bois.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir plante les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; de chaque côté de l'entrée. La caisse ouvre une bouche vers l'herbe. La trace du râteau passe à côté, vide. Pas de fer dans la porte. L'escargot s'engage, sans un bruit. Les pinces tiennent le rideau d'herbe. Le râteau, au mur, se tait. Un rayon de soleil s'arrête sur le bois.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Amir plante les &lt;emphasis&gt;pinces&lt;/emphasis&gt; de chaque côté de l'entrée. La caisse ouvre une bouche vers l'herbe. Le sillon du râteau passe à côté, vide. Pas de fer dans la porte. L'escargot s'engage, sans un bruit. Les pinces tiennent le rideau d'herbe. Le râteau, au mur, se tait. Un rai de soleil meurt sur le bois. [pause]</t>
+          <t>Amir plante les &lt;emphasis&gt;pinces&lt;/emphasis&gt; de chaque côté de l'entrée. La caisse ouvre une bouche vers l'herbe. La trace du râteau passe à côté, vide. Pas de fer dans la porte. L'escargot s'engage, sans un bruit. Les pinces tiennent le rideau d'herbe. Le râteau, au mur, se tait. Un rayon de soleil s'arrête sur le bois. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9593,12 +9593,12 @@
         <is>
           <t>narrateur|Amir plante les pinces de chaque côté de l'entrée.
 narrateur|La caisse ouvre une bouche vers l'herbe.
-narrateur|Le sillon du râteau passe à côté, vide.
+narrateur|La trace du râteau passe à côté, vide.
 enfant-m|Pas de fer dans la porte.
 narrateur|L'escargot s'engage, sans un bruit.
 maman|Les pinces tiennent le rideau d'herbe.
 papa|Le râteau, au mur, se tait.
-narrateur|Un rai de soleil meurt sur le bois.</t>
+narrateur|Un rayon de soleil s'arrête sur le bois.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -9630,17 +9630,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Amir écarte l'herbe à l'entrée, sans la casser. Les pinces tiennent ça ? Oui, pas de fer dans la porte. Le râteau a son mur, c'est mieux. Un rai meurt sur le seuil. Dedans, la caisse sent l'humide et le calme.</t>
+          <t>Amir écarte l'herbe à l'entrée, sans la casser. Les pinces tiennent ça ? Oui, pas de fer dans la porte. Le râteau a son mur, c'est mieux. Un rayon s'arrête sur le seuil. Dedans, la caisse sent l'humide et le calme.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir écarte l'herbe à l'entrée, sans la casser. Les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; tiennent ça ? Oui, pas de fer dans la porte. Le râteau a son mur, c'est mieux. Un rai meurt sur le seuil. Dedans, la caisse sent l'humide et le calme.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir écarte l'herbe à l'entrée, sans la casser. Les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; tiennent ça ? Oui, pas de fer dans la porte. Le râteau a son mur, c'est mieux. Un rayon s'arrête sur le seuil. Dedans, la caisse sent l'humide et le calme.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir écarte l'herbe à l'entrée, sans la casser. Les &lt;emphasis&gt;pinces&lt;/emphasis&gt; tiennent ça ? Oui, pas de fer dans la porte. Le râteau a son mur, c'est mieux. Un rai meurt sur le seuil. Dedans, la caisse sent l'humide et le calme.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir écarte l'herbe à l'entrée, sans la casser. Les &lt;emphasis&gt;pinces&lt;/emphasis&gt; tiennent ça ? Oui, pas de fer dans la porte. Le râteau a son mur, c'est mieux. Un rayon s'arrête sur le seuil. Dedans, la caisse sent l'humide et le calme.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
 papa|Les pinces tiennent ça ?
 enfant-m|Oui, pas de fer dans la porte.
 maman|Le râteau a son mur, c'est mieux.
-narrateur|Un rai meurt sur le seuil.
+narrateur|Un rayon s'arrête sur le seuil.
 narrateur|Dedans, la caisse sent l'humide et le calme.</t>
         </is>
       </c>
@@ -9815,17 +9815,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Amir attache la corde au rebord de la caisse. Il l'ancre dans le sillon du râteau. La grotte ne peut plus basculer. Elle est amarrée ! L'escargot entre, rassuré par l'immobilité. La corde a gagné contre le manche. Le fer dort au mur. Le bois ne tremble plus.</t>
+          <t>Amir attache la corde au rebord de la caisse. Il la fixe dans la trace du râteau. La grotte ne peut plus basculer. Elle est attachée ! L'escargot entre, rassuré : plus rien ne bouge. La corde a gagné contre le manche. Le fer dort au mur. Le bois ne tremble plus.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir attache la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; au rebord de la caisse. Il l'ancre dans le sillon du râteau. La grotte ne peut plus basculer. Elle est amarrée ! L'escargot entre, rassuré par l'immobilité. La corde a gagné contre le manche. Le fer dort au mur. Le bois ne tremble plus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir attache la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; au rebord de la caisse. Il la fixe dans la trace du râteau. La grotte ne peut plus basculer. Elle est attachée ! L'escargot entre, rassuré : plus rien ne bouge. La corde a gagné contre le manche. Le fer dort au mur. Le bois ne tremble plus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Amir attache la &lt;emphasis&gt;corde&lt;/emphasis&gt; au rebord de la caisse. Il l'ancre dans le sillon du râteau. La grotte ne peut plus basculer. Elle est amarrée ! L'escargot entre, rassuré par l'immobilité. La corde a gagné contre le manche. Le fer dort au mur. Le bois ne tremble plus. [pause]</t>
+          <t>Amir attache la &lt;emphasis&gt;corde&lt;/emphasis&gt; au rebord de la caisse. Il la fixe dans la trace du râteau. La grotte ne peut plus basculer. Elle est attachée ! L'escargot entre, rassuré : plus rien ne bouge. La corde a gagné contre le manche. Le fer dort au mur. Le bois ne tremble plus. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -9960,10 +9960,10 @@
       <c r="AW48" t="inlineStr">
         <is>
           <t>narrateur|Amir attache la corde au rebord de la caisse.
-narrateur|Il l'ancre dans le sillon du râteau.
+narrateur|Il la fixe dans la trace du râteau.
 narrateur|La grotte ne peut plus basculer.
-enfant-m|Elle est amarrée !
-narrateur|L'escargot entre, rassuré par l'immobilité.
+enfant-m|Elle est attachée !
+narrateur|L'escargot entre, rassuré : plus rien ne bouge.
 papa|La corde a gagné contre le manche.
 maman|Le fer dort au mur.
 narrateur|Le bois ne tremble plus.</t>
@@ -9998,17 +9998,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Amir appuie sur la caisse : rien ne bascule. Amarrée pour de bon ? La corde a gagné contre le manche. Le fer dort, le bois veille. Le sillon du râteau sert d'ancre, à présent. L'escargot n'entend plus le clac du fer.</t>
+          <t>Amir appuie sur la caisse : rien ne bascule. Attachée pour de bon ? La corde a gagné contre le manche. Le fer dort, le bois veille. La trace du râteau sert à tenir, maintenant. L'escargot n'entend plus le clac du fer.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir appuie sur la caisse : rien ne bascule. Amarrée pour de bon ? La &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; a gagné contre le manche. Le fer dort, le bois veille. Le sillon du râteau sert d'ancre, à présent. L'escargot n'entend plus le clac du fer.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir appuie sur la caisse : rien ne bascule. Attachée pour de bon ? La &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; a gagné contre le manche. Le fer dort, le bois veille. La trace du râteau sert à tenir, maintenant. L'escargot n'entend plus le clac du fer.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir appuie sur la caisse : rien ne bascule. Amarrée pour de bon ? La &lt;emphasis&gt;corde&lt;/emphasis&gt; a gagné contre le manche. Le fer dort, le bois veille. Le sillon du râteau sert d'ancre, à présent. L'escargot n'entend plus le clac du fer.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir appuie sur la caisse : rien ne bascule. Attachée pour de bon ? La &lt;emphasis&gt;corde&lt;/emphasis&gt; a gagné contre le manche. Le fer dort, le bois veille. La trace du râteau sert à tenir, maintenant. L'escargot n'entend plus le clac du fer.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
       <c r="AW49" t="inlineStr">
         <is>
           <t>narrateur|Amir appuie sur la caisse : rien ne bascule.
-papa|Amarrée pour de bon ?
+papa|Attachée pour de bon ?
 enfant-m|La corde a gagné contre le manche.
 maman|Le fer dort, le bois veille.
-narrateur|Le sillon du râteau sert d'ancre, à présent.
+narrateur|La trace du râteau sert à tenir, maintenant.
 narrateur|L'escargot n'entend plus le clac du fer.</t>
         </is>
       </c>
@@ -10936,17 +10936,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Amir pince un coin de chiffon à l'entrée de la caisse. Le chiffon sent la prune, un peu. Un rideau sucré ! L'escargot soulève le tissu, puis passe. Les pinces tiennent le parfum dehors. Le panier, sur le banc, garde le reste. Une tache violette sèche au soleil du banc. Dans la caisse, l'air reste neutre.</t>
+          <t>Amir pince un coin de chiffon à l'entrée de la caisse. Le chiffon sent la prune, un peu. Un rideau sucré ! L'escargot soulève le tissu, puis passe. Les pinces tiennent le parfum dehors. Le panier, sur le banc, garde le reste. Une tache violette sèche au soleil du banc. Dans la caisse, l'air n'a plus de fruit.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pince un coin de chiffon à l'entrée de la caisse. Le chiffon sent la prune, un peu. Un rideau sucré ! L'escargot soulève le tissu, puis passe. Les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; tiennent le parfum dehors. Le panier, sur le banc, garde le reste. Une tache violette sèche au soleil du banc. Dans la caisse, l'air reste neutre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pince un coin de chiffon à l'entrée de la caisse. Le chiffon sent la prune, un peu. Un rideau sucré ! L'escargot soulève le tissu, puis passe. Les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; tiennent le parfum dehors. Le panier, sur le banc, garde le reste. Une tache violette sèche au soleil du banc. Dans la caisse, l'air n'a plus de fruit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Amir pince un coin de chiffon à l'entrée de la caisse. Le chiffon sent la prune, un peu. Un rideau sucré ! L'escargot soulève le tissu, puis passe. Les &lt;emphasis&gt;pinces&lt;/emphasis&gt; tiennent le parfum dehors. Le panier, sur le banc, garde le reste. Une tache violette sèche au soleil du banc. Dans la caisse, l'air reste neutre. [pause]</t>
+          <t>Amir pince un coin de chiffon à l'entrée de la caisse. Le chiffon sent la prune, un peu. Un rideau sucré ! L'escargot soulève le tissu, puis passe. Les &lt;emphasis&gt;pinces&lt;/emphasis&gt; tiennent le parfum dehors. Le panier, sur le banc, garde le reste. Une tache violette sèche au soleil du banc. Dans la caisse, l'air n'a plus de fruit. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
 papa|Les pinces tiennent le parfum dehors.
 maman|Le panier, sur le banc, garde le reste.
 narrateur|Une tache violette sèche au soleil du banc.
-narrateur|Dans la caisse, l'air reste neutre.</t>
+narrateur|Dans la caisse, l'air n'a plus de fruit.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -11119,17 +11119,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Amir lève le rideau de chiffon, un millimètre. On dérange ? Non, je vérifie le parfum. Le sucre est resté sur le banc. Une tache violette sèche, loin de la caisse. Derrière le chiffon, l'air est plat, sans fruit.</t>
+          <t>Amir lève le rideau de chiffon, très peu. On dérange ? Non, je vérifie le parfum. Le sucre est resté sur le banc. Une tache violette sèche, loin de la caisse. Derrière le chiffon, l'air est plat, sans fruit.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir lève le rideau de chiffon, un millimètre. On dérange ? Non, je vérifie le parfum. Le sucre est resté sur le banc. Une tache violette sèche, loin de la caisse. Derrière le chiffon, l'air est plat, sans fruit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir lève le rideau de chiffon, très peu. On dérange ? Non, je vérifie le parfum. Le sucre est resté sur le banc. Une tache violette sèche, loin de la caisse. Derrière le chiffon, l'air est plat, sans fruit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir lève le rideau de chiffon, un millimètre. On dérange ? Non, je vérifie le parfum. Le sucre est resté sur le banc. Une tache violette sèche, loin de la caisse. Derrière le chiffon, l'air est plat, sans fruit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir lève le rideau de chiffon, très peu. On dérange ? Non, je vérifie le parfum. Le sucre est resté sur le banc. Une tache violette sèche, loin de la caisse. Derrière le chiffon, l'air est plat, sans fruit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|Amir lève le rideau de chiffon, un millimètre.
+          <t>narrateur|Amir lève le rideau de chiffon, très peu.
 papa|On dérange ?
 enfant-m|Non, je vérifie le parfum.
 maman|Le sucre est resté sur le banc.
@@ -11672,17 +11672,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Amir pose le seau en sentinelle devant la caisse. Le bleu sépare le bois du banc aux prunes. Personne ne roule dessus. L'escargot entre par le côté, loin du fruit. Le seau fait le garde. Les prunes font la confiture, plus tard. Une odeur sucrée s'arrête au bleu. Au fond de la caisse, la terre sent l'humide.</t>
+          <t>Amir pose le seau en garde devant la caisse. Le bleu sépare le bois du banc aux prunes. Personne ne roule dessus. L'escargot entre par le côté, loin du fruit. Le seau fait le garde. Les prunes font la confiture, plus tard. Une odeur sucrée s'arrête au bleu. Au fond de la caisse, la terre sent l'humide.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pose le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; en sentinelle devant la caisse. Le bleu sépare le bois du banc aux prunes. Personne ne roule dessus. L'escargot entre par le côté, loin du fruit. Le seau fait le garde. Les prunes font la confiture, plus tard. Une odeur sucrée s'arrête au bleu. Au fond de la caisse, la terre sent l'humide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pose le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; en garde devant la caisse. Le bleu sépare le bois du banc aux prunes. Personne ne roule dessus. L'escargot entre par le côté, loin du fruit. Le seau fait le garde. Les prunes font la confiture, plus tard. Une odeur sucrée s'arrête au bleu. Au fond de la caisse, la terre sent l'humide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Amir pose le &lt;emphasis&gt;seau&lt;/emphasis&gt; en sentinelle devant la caisse. Le bleu sépare le bois du banc aux prunes. Personne ne roule dessus. L'escargot entre par le côté, loin du fruit. Le seau fait le garde. Les prunes font la confiture, plus tard. Une odeur sucrée s'arrête au bleu. Au fond de la caisse, la terre sent l'humide. [pause]</t>
+          <t>Amir pose le &lt;emphasis&gt;seau&lt;/emphasis&gt; en garde devant la caisse. Le bleu sépare le bois du banc aux prunes. Personne ne roule dessus. L'escargot entre par le côté, loin du fruit. Le seau fait le garde. Les prunes font la confiture, plus tard. Une odeur sucrée s'arrête au bleu. Au fond de la caisse, la terre sent l'humide. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Amir pose le seau en sentinelle devant la caisse.
+          <t>narrateur|Amir pose le seau en garde devant la caisse.
 narrateur|Le bleu sépare le bois du banc aux prunes.
 enfant-m|Personne ne roule dessus.
 narrateur|L'escargot entre par le côté, loin du fruit.
@@ -11855,17 +11855,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Amir salue le seau-sentinelle d'un petit tapotement. Il laisse passer qui ? Lui, pas les prunes. La confiture attendra le soir. L'odeur sucrée s'arrête net au bleu. Au fond de la caisse, l'humide a gagné.</t>
+          <t>Amir salue le seau qui garde, d'un petit coup. Il laisse passer qui ? Lui, pas les prunes. La confiture attendra le soir. L'odeur sucrée s'arrête net au bleu. Au fond de la caisse, l'humide a gagné.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir salue le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;-sentinelle d'un petit tapotement. Il laisse passer qui ? Lui, pas les prunes. La confiture attendra le soir. L'odeur sucrée s'arrête net au bleu. Au fond de la caisse, l'humide a gagné.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir salue le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; qui garde, d'un petit coup. Il laisse passer qui ? Lui, pas les prunes. La confiture attendra le soir. L'odeur sucrée s'arrête net au bleu. Au fond de la caisse, l'humide a gagné.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir salue le &lt;emphasis&gt;seau&lt;/emphasis&gt;-sentinelle d'un petit tapotement. Il laisse passer qui ? Lui, pas les prunes. La confiture attendra le soir. L'odeur sucrée s'arrête net au bleu. Au fond de la caisse, l'humide a gagné.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir salue le &lt;emphasis&gt;seau&lt;/emphasis&gt; qui garde, d'un petit coup. Il laisse passer qui ? Lui, pas les prunes. La confiture attendra le soir. L'odeur sucrée s'arrête net au bleu. Au fond de la caisse, l'humide a gagné.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|Amir salue le seau-sentinelle d'un petit tapotement.
+          <t>narrateur|Amir salue le seau qui garde, d'un petit coup.
 papa|Il laisse passer qui ?
 enfant-m|Lui, pas les prunes.
 maman|La confiture attendra le soir.
@@ -13178,17 +13178,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Amir plante les pinces autour du creux mouillé. Elles tiennent un lambeau de torchon, juste assez. Un puits avec un chapeau ! L'escargot redescend vers l'eau, à l'ombre. Les pinces n'ont pas mouillé, elles. Tes bottes non plus, à présent. Le creux brille, petit miroir. Une corne y boit, ou presque.</t>
+          <t>Amir plante les pinces autour du creux mouillé. Elles tiennent un bout de torchon, juste assez. Un puits avec un chapeau ! L'escargot redescend vers l'eau, à l'ombre. Les pinces n'ont pas mouillé, elles. Tes bottes non plus, maintenant. Le creux brille, petit miroir. Une corne y boit, ou presque.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir plante les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; autour du creux mouillé. Elles tiennent un lambeau de torchon, juste assez. Un puits avec un chapeau ! L'escargot redescend vers l'eau, à l'ombre. Les pinces n'ont pas mouillé, elles. Tes bottes non plus, à présent. Le creux brille, petit miroir. Une corne y boit, ou presque.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir plante les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; autour du creux mouillé. Elles tiennent un bout de torchon, juste assez. Un puits avec un chapeau ! L'escargot redescend vers l'eau, à l'ombre. Les pinces n'ont pas mouillé, elles. Tes bottes non plus, maintenant. Le creux brille, petit miroir. Une corne y boit, ou presque.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Amir plante les &lt;emphasis&gt;pinces&lt;/emphasis&gt; autour du creux mouillé. Elles tiennent un lambeau de torchon, juste assez. Un puits avec un chapeau ! L'escargot redescend vers l'eau, à l'ombre. Les pinces n'ont pas mouillé, elles. Tes bottes non plus, à présent. Le creux brille, petit miroir. Une corne y boit, ou presque. [pause]</t>
+          <t>Amir plante les &lt;emphasis&gt;pinces&lt;/emphasis&gt; autour du creux mouillé. Elles tiennent un bout de torchon, juste assez. Un puits avec un chapeau ! L'escargot redescend vers l'eau, à l'ombre. Les pinces n'ont pas mouillé, elles. Tes bottes non plus, maintenant. Le creux brille, petit miroir. Une corne y boit, ou presque. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13323,11 +13323,11 @@
       <c r="AW66" t="inlineStr">
         <is>
           <t>narrateur|Amir plante les pinces autour du creux mouillé.
-narrateur|Elles tiennent un lambeau de torchon, juste assez.
+narrateur|Elles tiennent un bout de torchon, juste assez.
 enfant-m|Un puits avec un chapeau !
 narrateur|L'escargot redescend vers l'eau, à l'ombre.
 papa|Les pinces n'ont pas mouillé, elles.
-maman|Tes bottes non plus, à présent.
+maman|Tes bottes non plus, maintenant.
 narrateur|Le creux brille, petit miroir.
 narrateur|Une corne y boit, ou presque.</t>
         </is>
@@ -13546,17 +13546,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Amir tend la corde au-dessus du filet d'eau. Un coin de tissu y pend, comme un auvent. L'eau reste à lui. L'escargot longe le frais, sous le tissu. La corde fait le pont, sans bottes dessous. Au paillasson, le cuir sèche. Le filet ne part plus vers la porte. Il tourne autour de la feuille.</t>
+          <t>Amir tend la corde au-dessus du filet d'eau. Un coin de tissu y pend, comme un petit toit. L'eau reste à lui. L'escargot longe le frais, sous le tissu. La corde fait le pont, sans bottes dessous. Au paillasson, le cuir sèche. Le filet ne part plus vers la porte. Il tourne autour de la feuille.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir tend la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; au-dessus du filet d'eau. Un coin de tissu y pend, comme un auvent. L'eau reste à lui. L'escargot longe le frais, sous le tissu. La corde fait le pont, sans bottes dessous. Au paillasson, le cuir sèche. Le filet ne part plus vers la porte. Il tourne autour de la feuille.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir tend la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; au-dessus du filet d'eau. Un coin de tissu y pend, comme un petit toit. L'eau reste à lui. L'escargot longe le frais, sous le tissu. La corde fait le pont, sans bottes dessous. Au paillasson, le cuir sèche. Le filet ne part plus vers la porte. Il tourne autour de la feuille.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Amir tend la &lt;emphasis&gt;corde&lt;/emphasis&gt; au-dessus du filet d'eau. Un coin de tissu y pend, comme un auvent. L'eau reste à lui. L'escargot longe le frais, sous le tissu. La corde fait le pont, sans bottes dessous. Au paillasson, le cuir sèche. Le filet ne part plus vers la porte. Il tourne autour de la feuille. [pause]</t>
+          <t>Amir tend la &lt;emphasis&gt;corde&lt;/emphasis&gt; au-dessus du filet d'eau. Un coin de tissu y pend, comme un petit toit. L'eau reste à lui. L'escargot longe le frais, sous le tissu. La corde fait le pont, sans bottes dessous. Au paillasson, le cuir sèche. Le filet ne part plus vers la porte. Il tourne autour de la feuille. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       <c r="AW68" t="inlineStr">
         <is>
           <t>narrateur|Amir tend la corde au-dessus du filet d'eau.
-narrateur|Un coin de tissu y pend, comme un auvent.
+narrateur|Un coin de tissu y pend, comme un petit toit.
 enfant-m|L'eau reste à lui.
 narrateur|L'escargot longe le frais, sous le tissu.
 maman|La corde fait le pont, sans bottes dessous.
@@ -13729,17 +13729,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Amir suit l'eau du regard : elle tourne, elle reste. Plus de fuite vers la porte ? La corde a fermé le chemin des bottes. Le cuir peut sécher. Un auvent de tissu tremble, très peu. Autour de la feuille, le filet fait un collier.</t>
+          <t>Amir suit l'eau du regard : elle tourne, elle reste. Plus de fuite vers la porte ? La corde a fermé le chemin des bottes. Le cuir peut sécher. Un petit toit de tissu tremble, très peu. Autour de la feuille, le filet fait un collier.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir suit l'eau du regard : elle tourne, elle reste. Plus de fuite vers la porte ? La &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; a fermé le chemin des bottes. Le cuir peut sécher. Un auvent de tissu tremble, très peu. Autour de la feuille, le filet fait un collier.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir suit l'eau du regard : elle tourne, elle reste. Plus de fuite vers la porte ? La &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; a fermé le chemin des bottes. Le cuir peut sécher. Un petit toit de tissu tremble, très peu. Autour de la feuille, le filet fait un collier.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir suit l'eau du regard : elle tourne, elle reste. Plus de fuite vers la porte ? La &lt;emphasis&gt;corde&lt;/emphasis&gt; a fermé le chemin des bottes. Le cuir peut sécher. Un auvent de tissu tremble, très peu. Autour de la feuille, le filet fait un collier.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir suit l'eau du regard : elle tourne, elle reste. Plus de fuite vers la porte ? La &lt;emphasis&gt;corde&lt;/emphasis&gt; a fermé le chemin des bottes. Le cuir peut sécher. Un petit toit de tissu tremble, très peu. Autour de la feuille, le filet fait un collier.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -13881,7 +13881,7 @@
 papa|Plus de fuite vers la porte ?
 enfant-m|La corde a fermé le chemin des bottes.
 maman|Le cuir peut sécher.
-narrateur|Un auvent de tissu tremble, très peu.
+narrateur|Un petit toit de tissu tremble, très peu.
 narrateur|Autour de la feuille, le filet fait un collier.</t>
         </is>
       </c>
@@ -14667,17 +14667,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Amir pince un toit au-dessus du creux, hors du sillon. L'eau ne suit plus le fer. Elle reste en rond. L'escargot s'installe au bord, à l'ombre des pinces. Les pinces font un cercle, pas un fleuve. Le râteau, au mur, n'oriente plus l'eau. Une dent sèche capte la lumière, loin. Près de la feuille, tout est mat.</t>
+          <t>Amir pince un toit au-dessus du creux, hors de la trace. L'eau ne suit plus le fer. Elle reste en rond. L'escargot s'installe au bord, à l'ombre des pinces. Les pinces font un cercle, pas un fleuve. Le râteau, au mur, ne pousse plus l'eau. Une dent sèche capte la lumière, loin. Près de la feuille, tout est mat.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pince un toit au-dessus du creux, hors du sillon. L'eau ne suit plus le fer. Elle reste en rond. L'escargot s'installe au bord, à l'ombre des &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt;. Les pinces font un cercle, pas un fleuve. Le râteau, au mur, n'oriente plus l'eau. Une dent sèche capte la lumière, loin. Près de la feuille, tout est mat.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pince un toit au-dessus du creux, hors de la trace. L'eau ne suit plus le fer. Elle reste en rond. L'escargot s'installe au bord, à l'ombre des &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt;. Les pinces font un cercle, pas un fleuve. Le râteau, au mur, ne pousse plus l'eau. Une dent sèche capte la lumière, loin. Près de la feuille, tout est mat.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Amir pince un toit au-dessus du creux, hors du sillon. L'eau ne suit plus le fer. Elle reste en rond. L'escargot s'installe au bord, à l'ombre des &lt;emphasis&gt;pinces&lt;/emphasis&gt;. Les pinces font un cercle, pas un fleuve. Le râteau, au mur, n'oriente plus l'eau. Une dent sèche capte la lumière, loin. Près de la feuille, tout est mat. [pause]</t>
+          <t>Amir pince un toit au-dessus du creux, hors de la trace. L'eau ne suit plus le fer. Elle reste en rond. L'escargot s'installe au bord, à l'ombre des &lt;emphasis&gt;pinces&lt;/emphasis&gt;. Les pinces font un cercle, pas un fleuve. Le râteau, au mur, ne pousse plus l'eau. Une dent sèche capte la lumière, loin. Près de la feuille, tout est mat. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -14811,12 +14811,12 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Amir pince un toit au-dessus du creux, hors du sillon.
+          <t>narrateur|Amir pince un toit au-dessus du creux, hors de la trace.
 narrateur|L'eau ne suit plus le fer.
 enfant-m|Elle reste en rond.
 narrateur|L'escargot s'installe au bord, à l'ombre des pinces.
 maman|Les pinces font un cercle, pas un fleuve.
-papa|Le râteau, au mur, n'oriente plus l'eau.
+papa|Le râteau, au mur, ne pousse plus l'eau.
 narrateur|Une dent sèche capte la lumière, loin.
 narrateur|Près de la feuille, tout est mat.</t>
         </is>
@@ -14850,17 +14850,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Amir compare le cercle des pinces et le sillon vide. Rond contre ligne ? Le rond est pour lui, la ligne est finie. Le râteau n'écrit plus sur l'eau. Une dent sèche, au mur, garde un éclat. Près de la feuille, l'eau est mate, ronde, sage.</t>
+          <t>Amir compare le cercle des pinces et la trace vide. Rond contre ligne ? Le rond est pour lui, la ligne est finie. Le râteau n'écrit plus sur l'eau. Une dent sèche, au mur, garde un éclat. Près de la feuille, l'eau est mate, ronde, sage.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir compare le cercle des &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; et le sillon vide. Rond contre ligne ? Le rond est pour lui, la ligne est finie. Le râteau n'écrit plus sur l'eau. Une dent sèche, au mur, garde un éclat. Près de la feuille, l'eau est mate, ronde, sage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir compare le cercle des &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; et la trace vide. Rond contre ligne ? Le rond est pour lui, la ligne est finie. Le râteau n'écrit plus sur l'eau. Une dent sèche, au mur, garde un éclat. Près de la feuille, l'eau est mate, ronde, sage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir compare le cercle des &lt;emphasis&gt;pinces&lt;/emphasis&gt; et le sillon vide. Rond contre ligne ? Le rond est pour lui, la ligne est finie. Le râteau n'écrit plus sur l'eau. Une dent sèche, au mur, garde un éclat. Près de la feuille, l'eau est mate, ronde, sage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir compare le cercle des &lt;emphasis&gt;pinces&lt;/emphasis&gt; et la trace vide. Rond contre ligne ? Le rond est pour lui, la ligne est finie. Le râteau n'écrit plus sur l'eau. Une dent sèche, au mur, garde un éclat. Près de la feuille, l'eau est mate, ronde, sage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|Amir compare le cercle des pinces et le sillon vide.
+          <t>narrateur|Amir compare le cercle des pinces et la trace vide.
 papa|Rond contre ligne ?
 enfant-m|Le rond est pour lui, la ligne est finie.
 maman|Le râteau n'écrit plus sur l'eau.
@@ -15035,17 +15035,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Amir barre le sillon avec la corde, à plat. L'eau s'arrête et forme une mare. J'ai fermé la rivière ! L'escargot contourne la mare, sous un lambeau tendu. La corde a battu le manche. Le mur garde le fer. La mare tremble, puis se calme. Deux cornes s'y reflètent, un instant.</t>
+          <t>Amir barre la trace avec la corde, à plat. L'eau s'arrête et forme une mare. J'ai fermé la rivière ! L'escargot contourne la mare, sous un bout tendu. La corde a battu le manche. Le mur garde le fer. La mare tremble, puis se calme. Deux cornes s'y reflètent, un instant.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir barre le sillon avec la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt;, à plat. L'eau s'arrête et forme une mare. J'ai fermé la rivière ! L'escargot contourne la mare, sous un lambeau tendu. La corde a battu le manche. Le mur garde le fer. La mare tremble, puis se calme. Deux cornes s'y reflètent, un instant.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir barre la trace avec la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt;, à plat. L'eau s'arrête et forme une mare. J'ai fermé la rivière ! L'escargot contourne la mare, sous un bout tendu. La corde a battu le manche. Le mur garde le fer. La mare tremble, puis se calme. Deux cornes s'y reflètent, un instant.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Amir barre le sillon avec la &lt;emphasis&gt;corde&lt;/emphasis&gt;, à plat. L'eau s'arrête et forme une mare. J'ai fermé la rivière ! L'escargot contourne la mare, sous un lambeau tendu. La corde a battu le manche. Le mur garde le fer. La mare tremble, puis se calme. Deux cornes s'y reflètent, un instant. [pause]</t>
+          <t>Amir barre la trace avec la &lt;emphasis&gt;corde&lt;/emphasis&gt;, à plat. L'eau s'arrête et forme une mare. J'ai fermé la rivière ! L'escargot contourne la mare, sous un bout tendu. La corde a battu le manche. Le mur garde le fer. La mare tremble, puis se calme. Deux cornes s'y reflètent, un instant. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15179,10 +15179,10 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Amir barre le sillon avec la corde, à plat.
+          <t>narrateur|Amir barre la trace avec la corde, à plat.
 narrateur|L'eau s'arrête et forme une mare.
 enfant-m|J'ai fermé la rivière !
-narrateur|L'escargot contourne la mare, sous un lambeau tendu.
+narrateur|L'escargot contourne la mare, sous un bout tendu.
 papa|La corde a battu le manche.
 maman|Le mur garde le fer.
 narrateur|La mare tremble, puis se calme.
@@ -15218,17 +15218,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Amir se voit, un instant, dans la mare. Deux cornes aussi ? Oui, il est là, sous le lambeau. La corde a battu le fleuve du manche. La mare se calme, sans ride. Au mur, le fer n'oriente plus rien.</t>
+          <t>Amir se voit, un instant, dans la mare. Deux cornes aussi ? Oui, il est là, sous le tissu. La corde a battu le fleuve du manche. La mare se calme, sans ride. Au mur, le fer ne pousse plus l'eau.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir se voit, un instant, dans la mare. Deux cornes aussi ? Oui, il est là, sous le lambeau. La &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; a battu le fleuve du manche. La mare se calme, sans ride. Au mur, le fer n'oriente plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir se voit, un instant, dans la mare. Deux cornes aussi ? Oui, il est là, sous le tissu. La &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; a battu le fleuve du manche. La mare se calme, sans ride. Au mur, le fer ne pousse plus l'eau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir se voit, un instant, dans la mare. Deux cornes aussi ? Oui, il est là, sous le lambeau. La &lt;emphasis&gt;corde&lt;/emphasis&gt; a battu le fleuve du manche. La mare se calme, sans ride. Au mur, le fer n'oriente plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir se voit, un instant, dans la mare. Deux cornes aussi ? Oui, il est là, sous le tissu. La &lt;emphasis&gt;corde&lt;/emphasis&gt; a battu le fleuve du manche. La mare se calme, sans ride. Au mur, le fer ne pousse plus l'eau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15368,10 +15368,10 @@
         <is>
           <t>narrateur|Amir se voit, un instant, dans la mare.
 papa|Deux cornes aussi ?
-enfant-m|Oui, il est là, sous le lambeau.
+enfant-m|Oui, il est là, sous le tissu.
 maman|La corde a battu le fleuve du manche.
 narrateur|La mare se calme, sans ride.
-narrateur|Au mur, le fer n'oriente plus rien.</t>
+narrateur|Au mur, le fer ne pousse plus l'eau.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -15403,17 +15403,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Amir pose le seau en travers du sillon mort. L'eau s'y rassemble, fraîche. Un réservoir pour lui. L'escargot gravit le bord humide, puis s'abrite. Le seau capte ce que le râteau répandait. Échange réussi. Une goutte tombe dedans, ploc. Au mur, le fer reste sec.</t>
+          <t>Amir pose le seau en travers de la trace vide. L'eau s'y rassemble, fraîche. Un réservoir pour lui. L'escargot gravit le bord humide, puis s'abrite. Le seau capte ce que le râteau répandait. Échange réussi. Une goutte tombe dedans, ploc. Au mur, le fer reste sec.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pose le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; en travers du sillon mort. L'eau s'y rassemble, fraîche. Un réservoir pour lui. L'escargot gravit le bord humide, puis s'abrite. Le seau capte ce que le râteau répandait. Échange réussi. Une goutte tombe dedans, ploc. Au mur, le fer reste sec.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pose le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; en travers de la trace vide. L'eau s'y rassemble, fraîche. Un réservoir pour lui. L'escargot gravit le bord humide, puis s'abrite. Le seau capte ce que le râteau répandait. Échange réussi. Une goutte tombe dedans, ploc. Au mur, le fer reste sec.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Amir pose le &lt;emphasis&gt;seau&lt;/emphasis&gt; en travers du sillon mort. L'eau s'y rassemble, fraîche. Un réservoir pour lui. L'escargot gravit le bord humide, puis s'abrite. Le seau capte ce que le râteau répandait. Échange réussi. Une goutte tombe dedans, ploc. Au mur, le fer reste sec. [pause]</t>
+          <t>Amir pose le &lt;emphasis&gt;seau&lt;/emphasis&gt; en travers de la trace vide. L'eau s'y rassemble, fraîche. Un réservoir pour lui. L'escargot gravit le bord humide, puis s'abrite. Le seau capte ce que le râteau répandait. Échange réussi. Une goutte tombe dedans, ploc. Au mur, le fer reste sec. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Amir pose le seau en travers du sillon mort.
+          <t>narrateur|Amir pose le seau en travers de la trace vide.
 narrateur|L'eau s'y rassemble, fraîche.
 enfant-m|Un réservoir pour lui.
 narrateur|L'escargot gravit le bord humide, puis s'abrite.
@@ -16156,17 +16156,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Amir plante les pinces entre le creux et le banc. Un lambeau arrête les éclaboussures vers les prunes. L'eau d'un côté, le sucre de l'autre. L'escargot choisit le côté mouillé. Les pinces font la frontière. Le panier, au sec, se tait. Une prune roule sur le banc, sans tomber. Sous les pinces, la terre brille.</t>
+          <t>Amir plante les pinces entre le creux et le banc. Un bout de tissu arrête les gouttes vers les prunes. L'eau d'un côté, le sucre de l'autre. L'escargot choisit le côté mouillé. Les pinces font la frontière. Le panier, au sec, se tait. Une prune roule sur le banc, sans tomber. Sous les pinces, la terre brille.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir plante les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; entre le creux et le banc. Un lambeau arrête les éclaboussures vers les prunes. L'eau d'un côté, le sucre de l'autre. L'escargot choisit le côté mouillé. Les pinces font la frontière. Le panier, au sec, se tait. Une prune roule sur le banc, sans tomber. Sous les pinces, la terre brille.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir plante les &lt;emphasis level="moderate"&gt;pinces&lt;/emphasis&gt; entre le creux et le banc. Un bout de tissu arrête les gouttes vers les prunes. L'eau d'un côté, le sucre de l'autre. L'escargot choisit le côté mouillé. Les pinces font la frontière. Le panier, au sec, se tait. Une prune roule sur le banc, sans tomber. Sous les pinces, la terre brille.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Amir plante les &lt;emphasis&gt;pinces&lt;/emphasis&gt; entre le creux et le banc. Un lambeau arrête les éclaboussures vers les prunes. L'eau d'un côté, le sucre de l'autre. L'escargot choisit le côté mouillé. Les pinces font la frontière. Le panier, au sec, se tait. Une prune roule sur le banc, sans tomber. Sous les pinces, la terre brille. [pause]</t>
+          <t>Amir plante les &lt;emphasis&gt;pinces&lt;/emphasis&gt; entre le creux et le banc. Un bout de tissu arrête les gouttes vers les prunes. L'eau d'un côté, le sucre de l'autre. L'escargot choisit le côté mouillé. Les pinces font la frontière. Le panier, au sec, se tait. Une prune roule sur le banc, sans tomber. Sous les pinces, la terre brille. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16301,7 +16301,7 @@
       <c r="AW82" t="inlineStr">
         <is>
           <t>narrateur|Amir plante les pinces entre le creux et le banc.
-narrateur|Un lambeau arrête les éclaboussures vers les prunes.
+narrateur|Un bout de tissu arrête les gouttes vers les prunes.
 enfant-m|L'eau d'un côté, le sucre de l'autre.
 narrateur|L'escargot choisit le côté mouillé.
 papa|Les pinces font la frontière.
@@ -16524,17 +16524,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Amir tend la corde du creux jusqu'au tronc. Le lambeau fait un couloir, loin du banc. Son chemin à lui. L'escargot s'y engage, dos aux prunes. La corde l'éloigne du sucre. Le panier n'a plus à craindre l'eau. L'osier blanchit au soleil du banc. Le couloir, lui, reste sombre.</t>
+          <t>Amir tend la corde du creux jusqu'au tronc. Le bout de tissu fait un couloir, loin du banc. Son chemin à lui. L'escargot s'y engage, dos aux prunes. La corde l'éloigne du sucre. Le panier n'a plus à craindre l'eau. L'osier blanchit au soleil du banc. Le couloir, lui, reste sombre.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir tend la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; du creux jusqu'au tronc. Le lambeau fait un couloir, loin du banc. Son chemin à lui. L'escargot s'y engage, dos aux prunes. La corde l'éloigne du sucre. Le panier n'a plus à craindre l'eau. L'osier blanchit au soleil du banc. Le couloir, lui, reste sombre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir tend la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt; du creux jusqu'au tronc. Le bout de tissu fait un couloir, loin du banc. Son chemin à lui. L'escargot s'y engage, dos aux prunes. La corde l'éloigne du sucre. Le panier n'a plus à craindre l'eau. L'osier blanchit au soleil du banc. Le couloir, lui, reste sombre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Amir tend la &lt;emphasis&gt;corde&lt;/emphasis&gt; du creux jusqu'au tronc. Le lambeau fait un couloir, loin du banc. Son chemin à lui. L'escargot s'y engage, dos aux prunes. La corde l'éloigne du sucre. Le panier n'a plus à craindre l'eau. L'osier blanchit au soleil du banc. Le couloir, lui, reste sombre. [pause]</t>
+          <t>Amir tend la &lt;emphasis&gt;corde&lt;/emphasis&gt; du creux jusqu'au tronc. Le bout de tissu fait un couloir, loin du banc. Son chemin à lui. L'escargot s'y engage, dos aux prunes. La corde l'éloigne du sucre. Le panier n'a plus à craindre l'eau. L'osier blanchit au soleil du banc. Le couloir, lui, reste sombre. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16669,7 +16669,7 @@
       <c r="AW84" t="inlineStr">
         <is>
           <t>narrateur|Amir tend la corde du creux jusqu'au tronc.
-narrateur|Le lambeau fait un couloir, loin du banc.
+narrateur|Le bout de tissu fait un couloir, loin du banc.
 enfant-m|Son chemin à lui.
 narrateur|L'escargot s'y engage, dos aux prunes.
 maman|La corde l'éloigne du sucre.
@@ -16892,17 +16892,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Amir pose le seau entre le creux et les prunes. Le bleu coupe l'odeur sucrée. Deux mondes ! L'escargot entre du côté de l'eau. Le seau a choisi son camp. Les prunes aussi, sur leur banc. Une goutte chante dans le bleu. Sur le banc, une prune fendille, sans bruit.</t>
+          <t>Amir pose le seau entre le creux et les prunes. Le bleu coupe l'odeur sucrée. Deux mondes ! L'escargot entre du côté de l'eau. Le seau a choisi son camp. Les prunes aussi, sur leur banc. Une goutte chante dans le bleu. Sur le banc, une prune se fend, sans bruit.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pose le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; entre le creux et les prunes. Le bleu coupe l'odeur sucrée. Deux mondes ! L'escargot entre du côté de l'eau. Le seau a choisi son camp. Les prunes aussi, sur leur banc. Une goutte chante dans le bleu. Sur le banc, une prune fendille, sans bruit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir pose le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; entre le creux et les prunes. Le bleu coupe l'odeur sucrée. Deux mondes ! L'escargot entre du côté de l'eau. Le seau a choisi son camp. Les prunes aussi, sur leur banc. Une goutte chante dans le bleu. Sur le banc, une prune se fend, sans bruit.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Amir pose le &lt;emphasis&gt;seau&lt;/emphasis&gt; entre le creux et les prunes. Le bleu coupe l'odeur sucrée. Deux mondes ! L'escargot entre du côté de l'eau. Le seau a choisi son camp. Les prunes aussi, sur leur banc. Une goutte chante dans le bleu. Sur le banc, une prune fendille, sans bruit. [pause]</t>
+          <t>Amir pose le &lt;emphasis&gt;seau&lt;/emphasis&gt; entre le creux et les prunes. Le bleu coupe l'odeur sucrée. Deux mondes ! L'escargot entre du côté de l'eau. Le seau a choisi son camp. Les prunes aussi, sur leur banc. Une goutte chante dans le bleu. Sur le banc, une prune se fend, sans bruit. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17043,7 +17043,7 @@
 papa|Le seau a choisi son camp.
 maman|Les prunes aussi, sur leur banc.
 narrateur|Une goutte chante dans le bleu.
-narrateur|Sur le banc, une prune fendille, sans bruit.</t>
+narrateur|Sur le banc, une prune se fend, sans bruit.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -17075,17 +17075,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Amir pose une main sur le seau, une autre vers le banc. Deux mondes, tu disais. Oui, il a choisi l'eau. Les prunes fendillent, sans lui. Une goutte chante dans le bleu, une dernière fois. Sous le prunier, l'abri tient, et le soleil perd.</t>
+          <t>Amir pose une main sur le seau, une autre vers le banc. Deux mondes, tu disais. Oui, il a choisi l'eau. Les prunes se fendent, sans lui. Une goutte chante dans le bleu, une dernière fois. Sous le prunier, l'abri tient, et le soleil perd.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir pose une main sur le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;, une autre vers le banc. Deux mondes, tu disais. Oui, il a choisi l'eau. Les prunes fendillent, sans lui. Une goutte chante dans le bleu, une dernière fois. Sous le prunier, l'abri tient, et le soleil perd.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Amir pose une main sur le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;, une autre vers le banc. Deux mondes, tu disais. Oui, il a choisi l'eau. Les prunes se fendent, sans lui. Une goutte chante dans le bleu, une dernière fois. Sous le prunier, l'abri tient, et le soleil perd.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir pose une main sur le &lt;emphasis&gt;seau&lt;/emphasis&gt;, une autre vers le banc. Deux mondes, tu disais. Oui, il a choisi l'eau. Les prunes fendillent, sans lui. Une goutte chante dans le bleu, une dernière fois. Sous le prunier, l'abri tient, et le soleil perd.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Amir pose une main sur le &lt;emphasis&gt;seau&lt;/emphasis&gt;, une autre vers le banc. Deux mondes, tu disais. Oui, il a choisi l'eau. Les prunes se fendent, sans lui. Une goutte chante dans le bleu, une dernière fois. Sous le prunier, l'abri tient, et le soleil perd.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
           <t>narrateur|Amir pose une main sur le seau, une autre vers le banc.
 papa|Deux mondes, tu disais.
 enfant-m|Oui, il a choisi l'eau.
-maman|Les prunes fendillent, sans lui.
+maman|Les prunes se fendent, sans lui.
 narrateur|Une goutte chante dans le bleu, une dernière fois.
 narrateur|Sous le prunier, l'abri tient, et le soleil perd.</t>
         </is>
@@ -17254,7 +17254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17311,6 +17311,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
